--- a/data/trans_orig/IP16A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A05-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>21486</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41174</t>
+          <t>41114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>23749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67551</t>
+          <t>67288</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76378</t>
+          <t>75937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74067</t>
+          <t>73701</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82993</t>
+          <t>82671</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144759</t>
+          <t>144627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157255</t>
+          <t>157387</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18543</t>
+          <t>18461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>33341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>47923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54711</t>
+          <t>54751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>20777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>18427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33951</t>
+          <t>34454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108164</t>
+          <t>107949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118860</t>
+          <t>118705</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121786</t>
+          <t>122416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133189</t>
+          <t>133849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>234547</t>
+          <t>234044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250507</t>
+          <t>250071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>13488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>31217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10778</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>23308</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19649</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>39088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64878</t>
+          <t>64928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77458</t>
+          <t>76888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81385</t>
+          <t>81269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92910</t>
+          <t>92526</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149712</t>
+          <t>150182</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167175</t>
+          <t>167335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26173</t>
+          <t>25909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>33315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29109</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37195</t>
+          <t>36802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56919</t>
+          <t>58474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68470</t>
+          <t>68946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>34373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28216</t>
+          <t>29524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37430</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58313</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113467</t>
+          <t>113328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128752</t>
+          <t>128551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129750</t>
+          <t>128442</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>143967</t>
+          <t>143604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>247354</t>
+          <t>246860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268237</t>
+          <t>268895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>545</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18482</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>14142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28165</t>
+          <t>27279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69370</t>
+          <t>69187</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77774</t>
+          <t>77550</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68613</t>
+          <t>68923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79465</t>
+          <t>78522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140434</t>
+          <t>141320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154280</t>
+          <t>154457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20605</t>
+          <t>20094</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27417</t>
+          <t>26938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43819</t>
+          <t>43240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>52864</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>20678</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>22883</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>40249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105900</t>
+          <t>106783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117615</t>
+          <t>117900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99948</t>
+          <t>99360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113083</t>
+          <t>112829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>209885</t>
+          <t>210488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226989</t>
+          <t>227854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>22914</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>29864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>25047</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101426</t>
+          <t>100021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116875</t>
+          <t>116809</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111449</t>
+          <t>112128</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118362</t>
+          <t>118237</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214236</t>
+          <t>215820</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233290</t>
+          <t>233372</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34334</t>
+          <t>34438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40444</t>
+          <t>40241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38144</t>
+          <t>37642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45544</t>
+          <t>45496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75379</t>
+          <t>74383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84421</t>
+          <t>84267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>36075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151778</t>
+          <t>152429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169671</t>
+          <t>169731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165125</t>
+          <t>165638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176424</t>
+          <t>176747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>324139</t>
+          <t>323841</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342924</t>
+          <t>343685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A05-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4051</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5473</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,17%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4148</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18954</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20025</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16575</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21486</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17140</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21471</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,83%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18954</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16110</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41114</t>
+          <t>40998</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4798</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14199</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7832</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4770</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13419</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4400</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13132</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8832</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4998</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13968</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,07%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10989</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23749</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>78837</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>73470</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82871</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>72875</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>67288</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>75937</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>67575</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>76307</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>78837</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>73701</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>82671</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,93%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144627</t>
+          <t>144913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157387</t>
+          <t>157277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4547</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8418</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1301</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4090</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,77%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4547</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8695</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30719</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26848</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33291</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>21250</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18461</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18710</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,23%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,97%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>30719</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26571</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>33341</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,11%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>75,34%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>78</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47923</t>
+          <t>47305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54751</t>
+          <t>55152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9414</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21796</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11155</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6600</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17356</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6900</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17203</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14682</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9344</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20777</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34454</t>
+          <t>34274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>128511</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>121397</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>133779</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>114150</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>107949</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>118705</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>108102</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>118405</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,1%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>128511</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>122416</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>133849</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,75%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>234044</t>
+          <t>234224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250071</t>
+          <t>249934</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4321</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3834</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1666</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7287</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4012</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16196</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13179</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19227</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15774</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21395</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15322</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21321</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>83,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16196</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13488</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,55%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31217</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38110</t>
+          <t>38079</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>23061</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>23061</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>23061</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13482</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8563</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20015</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16464</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11348</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23308</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11050</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23273</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13482</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8508</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19765</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21935</t>
+          <t>22978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39088</t>
+          <t>39427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>87552</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>81019</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92471</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>71772</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>64928</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76888</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>64963</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>77186</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>81,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>87552</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>81269</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>92526</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,66%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150182</t>
+          <t>149843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167335</t>
+          <t>166292</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>87,86%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5679</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2334</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10392</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6077</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3089</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10495</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10639</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,69%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5679</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2631</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10039</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33754</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29041</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37099</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>30327</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25909</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33315</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>33599</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,31%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>71,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33754</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>29394</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>36802</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>85,6%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58474</t>
+          <t>57783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68946</t>
+          <t>68951</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13930</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28618</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>26375</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19150</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34373</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19018</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35328</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20465</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14362</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29524</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>37446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58807</t>
+          <t>58597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>137501</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>129348</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>144036</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>121326</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>113328</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>128551</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>112373</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>128683</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,14%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>137501</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>128442</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>143604</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,04%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246860</t>
+          <t>247070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268895</t>
+          <t>268221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147701</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1964</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5295</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5034</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>12,52%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>3,48%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3035</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8121</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13727</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10396</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15146</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10657</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15144</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>87,48%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>67,92%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>96,52%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8121</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5751</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,43%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>30</t>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23830</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11031</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6384</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16795</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8737</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5429</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13792</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13923</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11031</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7098</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16697</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,88%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>26503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74589</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>68825</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>79236</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>74242</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>69187</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>77550</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>69056</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>78371</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>74589</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>68923</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>78522</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,12%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141320</t>
+          <t>142096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154457</t>
+          <t>154887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4620,67 +4620,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8135</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>4194</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7993</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7922</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4362</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8776</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24508</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20735</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26899</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>71,82%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>24598</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20799</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27300</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20870</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>27064</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>85,43%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24508</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20094</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>26938</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43240</t>
+          <t>43383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52864</t>
+          <t>52822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4963,67 +4963,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10764</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23141</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>14895</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9561</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20678</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9591</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21149</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16058</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10447</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23916</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22883</t>
+          <t>23666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>40267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>107218</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100135</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>112512</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>112566</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>106783</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>117900</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>106312</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>117870</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>107218</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>99360</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>112829</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,97%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>210488</t>
+          <t>210470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227854</t>
+          <t>227071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5041</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>36,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1843</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5161</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12061</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8879</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>63,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13387</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10069</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>87,9%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27254</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>22517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7071</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9533</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4034</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20822</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7896</t>
+          <t>12058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25047</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>104462</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100841</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>106461</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>111310</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>100021</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>116809</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>115929</t>
+          <t>85712</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112128</t>
+          <t>80626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118237</t>
+          <t>89070</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>227239</t>
+          <t>190174</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>215820</t>
+          <t>184346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233372</t>
+          <t>194228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8532</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3637</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7204</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13770</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39494</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34587</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42182</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>38005</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34438</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>40241</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42608</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37642</t>
+          <t>33926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45496</t>
+          <t>39455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>80613</t>
+          <t>76639</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74383</t>
+          <t>70475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84267</t>
+          <t>79988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8935</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15696</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15013</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7984</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25286</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36075</t>
+          <t>28753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>156017</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149256</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>160294</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>162702</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>152429</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>169731</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>172403</t>
+          <t>131080</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165638</t>
+          <t>124753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176747</t>
+          <t>135330</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>335104</t>
+          <t>287098</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323841</t>
+          <t>279191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343685</t>
+          <t>293780</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
